--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="524">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:40:58+00:00</t>
+    <t>2026-07-29T17:09:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -857,7 +857,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
 </t>
   </si>
   <si>
@@ -1627,10 +1627,14 @@
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
-    <t>Référence vers la ressource Patient titulaire du dossier.</t>
+    <t>Référence vers la ressource Patient titulaire du dossier. Conformément à IHE MHD ITI-105, lorsque fournie, cette référence pointe une ressource Patient contenue (contained). Selon le statut d'identité, la ressource est conforme au profil FR Core Patient (identité non qualifiée) ou FR Core Patient INS (identité qualifiée, matricule INS + traits INSi).</t>
   </si>
   <si>
     <t>The Patient Information as known when the document was published. May be a reference to a version specific, or contained.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), c'est-à-dire une référence interne commençant par '#' (IHE MHD ITI-105 §2:3.105.4.1.2.2). {context.sourcePatientInfo.reference.exists() implies context.sourcePatientInfo.reference.startsWith('#')}</t>
   </si>
   <si>
     <t>DocumentEntry.sourcePatientInfo, DocumentEntry.sourcePatientId</t>
@@ -9736,7 +9740,7 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>513</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9757,15 +9761,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9788,16 +9792,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9847,7 +9851,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9865,13 +9869,13 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9880,7 +9884,7 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:09:31+00:00</t>
+    <t>2026-07-30T07:55:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -857,7 +857,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1627,7 +1627,7 @@
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
-    <t>Référence vers la ressource Patient titulaire du dossier. Conformément à IHE MHD ITI-105, lorsque fournie, cette référence pointe une ressource Patient contenue (contained). Selon le statut d'identité, la ressource est conforme au profil FR Core Patient (identité non qualifiée) ou FR Core Patient INS (identité qualifiée, matricule INS + traits INSi).</t>
+    <t>Référence vers la ressource Patient titulaire du dossier. Conformément à IHE MHD ITI-105, lorsque fournie, cette référence pointe une ressource Patient contenue (contained). Selon le statut d'identité, la ressource est conforme au profil FR Core Patient (identité non qualifiée) ou FR Core Patient INS (identité qualifiée, matricule INS + traits INSi) qui hérite de profil FR Core Patient.</t>
   </si>
   <si>
     <t>The Patient Information as known when the document was published. May be a reference to a version specific, or contained.</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:55:20+00:00</t>
+    <t>2026-07-30T08:19:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1634,7 +1634,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), c'est-à-dire une référence interne commençant par '#' (IHE MHD ITI-105 §2:3.105.4.1.2.2). {context.sourcePatientInfo.reference.exists() implies context.sourcePatientInfo.reference.startsWith('#')}</t>
+constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), c'est-à-dire une référence interne commençant par '#' (IHE MHD ITI-105 §2:3.105.4.1.2.2). {reference.exists() implies reference.startsWith('#')}</t>
   </si>
   <si>
     <t>DocumentEntry.sourcePatientInfo, DocumentEntry.sourcePatientId</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:19:35+00:00</t>
+    <t>2026-07-30T08:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="525">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:31:43+00:00</t>
+    <t>2026-07-30T10:07:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1625,6 +1625,10 @@
   </si>
   <si>
     <t>DocumentReference.context.sourcePatientInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient) &lt;&lt;contained&gt;&gt;
+</t>
   </si>
   <si>
     <t>Référence vers la ressource Patient titulaire du dossier. Conformément à IHE MHD ITI-105, lorsque fournie, cette référence pointe une ressource Patient contenue (contained). Selon le statut d'identité, la ressource est conforme au profil FR Core Patient (identité non qualifiée) ou FR Core Patient INS (identité qualifiée, matricule INS + traits INSi) qui hérite de profil FR Core Patient.</t>
@@ -9671,13 +9675,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>267</v>
+        <v>511</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9740,7 +9744,7 @@
         <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>80</v>
@@ -9761,15 +9765,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9792,16 +9796,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9851,7 +9855,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9869,13 +9873,13 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9884,7 +9888,7 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>

--- a/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/cp-ins-iti-105/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:07:17+00:00</t>
+    <t>2026-07-30T12:04:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1638,7 +1638,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), c'est-à-dire une référence interne commençant par '#' (IHE MHD ITI-105 §2:3.105.4.1.2.2). {reference.exists() implies reference.startsWith('#')}</t>
+constr-sp-sourcePatientInfo-contained:Lorsqu'il est fourni, context.sourcePatientInfo doit référencer une ressource Patient contenue (contained), cf spécifications IHE MHD ITI-105 §2:3.105.4.1.2.2. {reference.exists() implies reference.startsWith('#')}</t>
   </si>
   <si>
     <t>DocumentEntry.sourcePatientInfo, DocumentEntry.sourcePatientId</t>
